--- a/Design_Docs/Instruction_Word_Table.xlsx
+++ b/Design_Docs/Instruction_Word_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\Design_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BC5CEA-46F7-4869-B925-952022FB4104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="45972" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>

--- a/Design_Docs/Instruction_Word_Table.xlsx
+++ b/Design_Docs/Instruction_Word_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\Design_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BC5CEA-46F7-4869-B925-952022FB4104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982A2A79-3EAA-4BB9-86BC-1D4C701E7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="45984" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>

--- a/Design_Docs/Instruction_Word_Table.xlsx
+++ b/Design_Docs/Instruction_Word_Table.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,12 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982A2A79-3EAA-4BB9-86BC-1D4C701E7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45984" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="5280" yWindow="2080" windowWidth="20320" windowHeight="11720" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Design_Docs/Instruction_Word_Table.xlsx
+++ b/Design_Docs/Instruction_Word_Table.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\Design_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982A2A79-3EAA-4BB9-86BC-1D4C701E7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431176F9-152D-4D0B-BDE9-B20732E49C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="2080" windowWidth="20320" windowHeight="11720" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
